--- a/docs/feedback-tracker.xlsx
+++ b/docs/feedback-tracker.xlsx
@@ -1185,20 +1185,28 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>추가한 20편이 16·17절 집계와 부록 목록(237편)에 빠져 있음 — 실제 257편</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n"/>
+          <t>16·17절 집계와 부록에 20편 추가(237 → 257편), 19절 교차참조 제14절 → 제18절</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>진행보고 v1.9 16·17절 · 부록 1·2</t>
+        </is>
+      </c>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>미착수</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>다음 판에서 집계·부록 갱신</t>
+          <t>16절 표 A·D 영역 수치와 묶음 수(18 → 19개) 오류도 함께 바로잡음</t>
         </is>
       </c>
     </row>

--- a/docs/feedback-tracker.xlsx
+++ b/docs/feedback-tracker.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>진행보고 v1.9 7~10절 · 변수구성_최대안 v1.0</t>
+          <t>진행보고 v2.0 7~10절 · 변수구성_최대안 v1.0</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>진행보고 v1.9 11절 · EMS입력_윈도우분석.xlsx</t>
+          <t>진행보고 v2.0 11절 · EMS입력_윈도우분석.xlsx</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>진행보고 v1.9 13절 · build_cost_vars.py</t>
+          <t>진행보고 v2.0 13절 · build_cost_vars.py</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>진행보고 v1.9 13절 · 이중계상_처리방식_비교.xlsx</t>
+          <t>진행보고 v2.0 13절 · 이중계상_처리방식_비교.xlsx</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>진행보고 v1.9 14~15절 · 분석모형_전수검토 v1.0 · sfa.py</t>
+          <t>진행보고 v2.0 14~15절 · 분석모형_전수검토 v1.0 · sfa.py</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>진행보고 v1.9 18절</t>
+          <t>진행보고 v2.0 18절</t>
         </is>
       </c>
       <c r="H11" s="4" t="n"/>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>진행보고 v1.9 3~4절 · 근거이론_구성 v1.1</t>
+          <t>진행보고 v2.0 3~4절 · 근거이론_구성 v1.1</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>진행보고 v1.9 16·17절 · 부록 1·2</t>
+          <t>진행보고 v2.0 16·17절 · 부록 1·2</t>
         </is>
       </c>
       <c r="H15" s="4" t="n"/>
@@ -1215,32 +1215,96 @@
         <f>IF(D16="","",ROW()-3)</f>
         <v/>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>지도교수</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>논문 쓴 거 내일(9. 29.)까지 보내주기 — 교수님 메일</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>진행보고·원고</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>분석 자료·진행보고·집필 현황 3종 준비, 메일 최종본 작성</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>분석 자료 v1.5 · 진행보고 v2.0 · 집필 현황 v1.0</t>
+        </is>
+      </c>
       <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>진행 중</t>
+        </is>
+      </c>
       <c r="J16" s="4" t="n"/>
-      <c r="K16" s="5" t="n"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>발송은 직접 — 기한 9. 29.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4">
         <f>IF(D17="","",ROW()-3)</f>
         <v/>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>지도교수</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>일정 잡기 — 면담 일시</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>면담</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>메일에 후보 일시 자리를 마련, 집필 일정(안) 작성</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>집필 현황 v1.0 · 메일 최종본</t>
+        </is>
+      </c>
       <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>미착수</t>
+        </is>
+      </c>
       <c r="J17" s="4" t="n"/>
-      <c r="K17" s="5" t="n"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>후보 일시 세 개 미정, 교수님 회신 뒤 확정</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4">

--- a/docs/feedback-tracker.xlsx
+++ b/docs/feedback-tracker.xlsx
@@ -1248,13 +1248,17 @@
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>진행 중</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="n"/>
+          <t>완료</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>발송은 직접 — 기한 9. 29.</t>
+          <t>메일 송부 완료(9. 29.) — 첨부 3종</t>
         </is>
       </c>
     </row>
@@ -1296,13 +1300,13 @@
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>진행 중</t>
         </is>
       </c>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>후보 일시 세 개 미정, 교수님 회신 뒤 확정</t>
+          <t>교수님 회신 대기 — 면담 일시는 회신 뒤 확정</t>
         </is>
       </c>
     </row>

--- a/docs/feedback-tracker.xlsx
+++ b/docs/feedback-tracker.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>검토 요청</t>
+          <t>보류</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>주 분석은 3 × 4, 최대안은 민감도로 제안 — 확인 요청 둘째</t>
+          <t>주 분석은 3 × 4, 최대안은 민감도로 제안 — 확인 요청 둘째 · 9. 29. 지시(통계 중단)로 주제 확정 때까지 보류</t>
         </is>
       </c>
     </row>
@@ -704,13 +704,13 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>진행 중</t>
+          <t>보류</t>
         </is>
       </c>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>남은 일: EMS 로 직접 돌려 결과 대조, 창 너비 확정(확인 요청 여덟째)</t>
+          <t>남은 일: EMS 로 직접 돌려 결과 대조, 창 너비 확정(확인 요청 여덟째) · 9. 29. 지시(통계 중단)로 주제 확정 때까지 보류</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>검토 요청</t>
+          <t>보류</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>본회계 투입(M1) 채택 여부 — 확인 요청 열째</t>
+          <t>본회계 투입(M1) 채택 여부 — 확인 요청 열째 · 9. 29. 지시(통계 중단)로 주제 확정 때까지 보류</t>
         </is>
       </c>
     </row>
@@ -860,13 +860,13 @@
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>보류</t>
         </is>
       </c>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>「대폭 보강」의 비목 단위 보강은 아직 — 현재는 회계 단위 분해까지</t>
+          <t>「대폭 보강」의 비목 단위 보강은 아직 — 현재는 회계 단위 분해까지 · 9. 29. 지시(통계 중단)로 주제 확정 때까지 보류</t>
         </is>
       </c>
     </row>
@@ -1008,13 +1008,13 @@
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>검토 요청</t>
+          <t>보류</t>
         </is>
       </c>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>확인 요청 열한째</t>
+          <t>확인 요청 열한째 · 9. 29. 지시(통계 중단)로 주제 확정 때까지 보류</t>
         </is>
       </c>
     </row>
@@ -1052,13 +1052,13 @@
       <c r="H12" s="4" t="n"/>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>미착수</t>
+          <t>보류</t>
         </is>
       </c>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>SFA 가 주 모형이 되면 착수. 투입가격은 Izadi 외(2002) 근거로 생략 중</t>
+          <t>SFA 가 주 모형이 되면 착수. 투입가격은 Izadi 외(2002) 근거로 생략 중 · 9. 29. 지시(통계 중단)로 주제 확정 때까지 보류</t>
         </is>
       </c>
     </row>
@@ -1315,80 +1315,268 @@
         <f>IF(D18="","",ROW()-3)</f>
         <v/>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="5" t="n"/>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>지도교수</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>(총평) 통계가 목적이 아님 — 제목·분석이 비슷한 논문이 있는지, 그와 무엇이 다른지가 핵심. 남이 한 연구를 다시 돌리면 석사논문</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>제목 · 제1장</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>현재 제목 다섯 요소가 모두 선행연구와 겹침을 점검(국내 55편, 그중 박사 15편 — 새로운 것은 분석 기간뿐). 물음을 「지역 단위 재정 배분 전제의 검증」으로 옮기고 제목 후보 3개 제시(① 권고)</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>연구진술문_차별성 v1.0 5~6절</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>a557316</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>검토 요청</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>연구 방향과 제목은 교수님 확인 필요 — 8절 여쭐 것 첫째·셋째</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4">
         <f>IF(D19="","",ROW()-3)</f>
         <v/>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="5" t="n"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>지도교수</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>① 박사연구가 해결할 사회적 문제, 왜 연구하는지(연구진술문)를 아주 구체적으로</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>제1장 서론</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>RISE → ANCHOR 의 시·도 단위 배분(1조 9,410억 → 2조 1,403억)이 기대는 두 전제와 전제가 틀렸을 때의 비용, 예비 검토(격차의 71.8% 개별 대학 · 3.0% 시·도), 강원·제주의 역설, 연구문제 3개로 재설정</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>연구진술문_차별성 v1.0 2~3절</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>a557316</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>검토 요청</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>학령인구·미충원 규모는 통계청·대학알리미 공표치로 보강 예정</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4">
         <f>IF(D20="","",ROW()-3)</f>
         <v/>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="5" t="n"/>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>지도교수</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>② 기존 논문과 다른 본인만의 관점(이론) — 기존 교육재정 논문과 여러 각도에서 집중 비교 (교수님이 가장 보고 싶은 부분)</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>제2장 · 제1장</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>차별성 여섯 각도(물음 · 격차를 보는 방식 · 정책 · 교육재정의 축 · 이론 · 방법). 장소 기반 정책 논쟁 + 생태학적 오류를 중심 관점으로, 교육재정 문헌 5편과 비교, 가장 가까운 선행연구 이창원·김한나(2025) 명시, 이론 11개 재배치</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>연구진술문_차별성 v1.0 4절 · 콘솔 문헌 D5·D6 묶음(266편)</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>a557316 · 45567a5</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>검토 요청</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>선행연구 6편 본문 확인 필요 — 8절 여쭐 것 둘째</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4">
         <f>IF(D21="","",ROW()-3)</f>
         <v/>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>지도교수</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>③ 통계는 더 이상 돌리지 말고 서론과 차별성을 집중적으로 써서 제출</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>제출</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>서론(연구진술문)과 차별성 문서 작성 — 한글 약 7,600자 · 표 5개, 새 통계 분석 없음(인용 수치는 진행보고 v2.0 12절)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>박사학위논문_연구진술문_차별성_석재영_v1.0.hwpx</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>a557316</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>진행 중</t>
+        </is>
+      </c>
       <c r="J21" s="4" t="n"/>
-      <c r="K21" s="5" t="n"/>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>문서 작성 완료(9. 29.) — 교수님께 제출 필요</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4">
         <f>IF(D22="","",ROW()-3)</f>
         <v/>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>지도교수</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>④ 논문 주제가 명확히 잡히기 전에는 통계를 돌리지 말 것</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>분석 전체</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>분석에 딸린 항목(1·2·4·5·8·9번 — 변수 개수, 윈도우 EMS, 이중 계상, 세출 비목 재파싱, SFA 위상, 패널 SFA)을 주제 확정 때까지 보류</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>이 반영표 1·2·4·5·8·9번 · 연구진술문_차별성 v1.0 7절</t>
+        </is>
+      </c>
       <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>진행 중</t>
+        </is>
+      </c>
       <c r="J22" s="4" t="n"/>
-      <c r="K22" s="5" t="n"/>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>주제 확정 때까지 유지</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4">
